--- a/REST7.xlsx
+++ b/REST7.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunuss\ErpGüzelTeknoloji\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunuss\ErpGüzelteknoloji\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -768,13 +768,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1648,22 +1648,22 @@
       <c r="A1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="14"/>
@@ -1691,7 +1691,7 @@
       <c r="W2" s="14"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1738,7 +1738,7 @@
       </c>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="15"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1808,7 +1808,7 @@
       <c r="W5" s="14"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1837,7 +1837,7 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="15"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="9">
         <v>1</v>
       </c>
@@ -1889,7 +1889,7 @@
       <c r="W8" s="14"/>
     </row>
     <row r="9" spans="1:23">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1915,7 +1915,7 @@
       </c>
     </row>
     <row r="10" spans="1:23">
-      <c r="A10" s="15"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="9">
         <v>1</v>
       </c>
@@ -1964,7 +1964,7 @@
       <c r="W11" s="14"/>
     </row>
     <row r="12" spans="1:23">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="13" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2029,7 +2029,7 @@
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="15"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="W14" s="14"/>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>105</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2168,7 +2168,7 @@
       <c r="Q15" s="7"/>
     </row>
     <row r="16" spans="1:23">
-      <c r="A16" s="15"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="9">
         <v>1</v>
       </c>
@@ -2241,7 +2241,7 @@
       <c r="W17" s="14"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2270,7 +2270,7 @@
       </c>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="15"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="9">
         <v>1</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="W20" s="14"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2393,7 +2393,7 @@
       </c>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" s="15"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="9">
         <v>1</v>
       </c>
@@ -2462,7 +2462,7 @@
       </c>
     </row>
     <row r="23" spans="1:24">
-      <c r="A23" s="15"/>
+      <c r="A23" s="13"/>
       <c r="B23" s="11">
         <v>2</v>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="W24" s="14"/>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2610,7 +2610,7 @@
       <c r="X25" s="7"/>
     </row>
     <row r="26" spans="1:24">
-      <c r="A26" s="15"/>
+      <c r="A26" s="13"/>
       <c r="B26" s="9">
         <v>1</v>
       </c>
@@ -2656,7 +2656,7 @@
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="15"/>
+      <c r="A27" s="13"/>
       <c r="B27" s="11">
         <v>2</v>
       </c>
@@ -2727,7 +2727,7 @@
       <c r="W28" s="14"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="13" t="s">
         <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2783,7 +2783,7 @@
       <c r="X29" s="7"/>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" s="15"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="9">
         <v>1</v>
       </c>
@@ -2826,7 +2826,7 @@
       <c r="V30" s="1"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="15"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="11">
         <v>2</v>
       </c>
@@ -2894,7 +2894,7 @@
       <c r="W32" s="14"/>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="13" t="s">
         <v>199</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -2944,7 +2944,7 @@
       <c r="X33" s="7"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="15"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="9">
         <v>1</v>
       </c>
@@ -2971,7 +2971,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="15"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="11">
         <v>2</v>
       </c>
@@ -2999,6 +2999,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A17:W17"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A5:W5"/>
+    <mergeCell ref="A8:W8"/>
+    <mergeCell ref="A11:W11"/>
+    <mergeCell ref="A14:W14"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A33:A35"/>
@@ -3007,19 +3020,6 @@
     <mergeCell ref="A28:W28"/>
     <mergeCell ref="A32:W32"/>
     <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A17:W17"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A5:W5"/>
-    <mergeCell ref="A8:W8"/>
-    <mergeCell ref="A11:W11"/>
-    <mergeCell ref="A14:W14"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>

--- a/REST7.xlsx
+++ b/REST7.xlsx
@@ -768,13 +768,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1625,19 +1625,21 @@
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="41.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="33.36328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
@@ -1648,22 +1650,22 @@
       <c r="A1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="14"/>
@@ -1691,7 +1693,7 @@
       <c r="W2" s="14"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1738,7 +1740,7 @@
       </c>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="13"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1808,7 +1810,7 @@
       <c r="W5" s="14"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="15" t="s">
         <v>90</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1837,7 +1839,7 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="9">
         <v>1</v>
       </c>
@@ -1889,7 +1891,7 @@
       <c r="W8" s="14"/>
     </row>
     <row r="9" spans="1:23">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1915,7 +1917,7 @@
       </c>
     </row>
     <row r="10" spans="1:23">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="9">
         <v>1</v>
       </c>
@@ -1964,7 +1966,7 @@
       <c r="W11" s="14"/>
     </row>
     <row r="12" spans="1:23">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="15" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2029,7 +2031,7 @@
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -2117,7 +2119,7 @@
       <c r="W14" s="14"/>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="15" t="s">
         <v>105</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2168,7 +2170,7 @@
       <c r="Q15" s="7"/>
     </row>
     <row r="16" spans="1:23">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="9">
         <v>1</v>
       </c>
@@ -2241,7 +2243,7 @@
       <c r="W17" s="14"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="15" t="s">
         <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2270,7 +2272,7 @@
       </c>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="9">
         <v>1</v>
       </c>
@@ -2322,7 +2324,7 @@
       <c r="W20" s="14"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="15" t="s">
         <v>157</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2393,7 +2395,7 @@
       </c>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="9">
         <v>1</v>
       </c>
@@ -2462,7 +2464,7 @@
       </c>
     </row>
     <row r="23" spans="1:24">
-      <c r="A23" s="13"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="11">
         <v>2</v>
       </c>
@@ -2556,7 +2558,7 @@
       <c r="W24" s="14"/>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="15" t="s">
         <v>167</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2610,7 +2612,7 @@
       <c r="X25" s="7"/>
     </row>
     <row r="26" spans="1:24">
-      <c r="A26" s="13"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="9">
         <v>1</v>
       </c>
@@ -2656,7 +2658,7 @@
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="11">
         <v>2</v>
       </c>
@@ -2727,7 +2729,7 @@
       <c r="W28" s="14"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="15" t="s">
         <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2783,7 +2785,7 @@
       <c r="X29" s="7"/>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="9">
         <v>1</v>
       </c>
@@ -2826,7 +2828,7 @@
       <c r="V30" s="1"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="11">
         <v>2</v>
       </c>
@@ -2894,7 +2896,7 @@
       <c r="W32" s="14"/>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="15" t="s">
         <v>199</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -2944,7 +2946,7 @@
       <c r="X33" s="7"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="9">
         <v>1</v>
       </c>
@@ -2971,7 +2973,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="11">
         <v>2</v>
       </c>
@@ -2999,6 +3001,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A20:W20"/>
+    <mergeCell ref="A24:W24"/>
+    <mergeCell ref="A28:W28"/>
+    <mergeCell ref="A32:W32"/>
+    <mergeCell ref="A21:A23"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A6:A7"/>
@@ -3012,14 +3022,6 @@
     <mergeCell ref="A14:W14"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A20:W20"/>
-    <mergeCell ref="A24:W24"/>
-    <mergeCell ref="A28:W28"/>
-    <mergeCell ref="A32:W32"/>
-    <mergeCell ref="A21:A23"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
